--- a/informes_data/Primera FEB/2025-26/playoffs/individual/NP_play_by_play_2513257_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/playoffs/individual/NP_play_by_play_2513257_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4247</v>
+        <v>5.0201</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7225</v>
+        <v>4.3179</v>
       </c>
       <c r="F2" t="n">
         <v>0.7022</v>
@@ -610,10 +610,10 @@
         <v>0.4405</v>
       </c>
       <c r="S2" t="n">
-        <v>1.67</v>
+        <v>1.2654</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3622</v>
+        <v>0.9576</v>
       </c>
       <c r="U2" t="n">
         <v>0.3079</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7885</v>
+        <v>3.5051</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1298</v>
+        <v>1.6734</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6588</v>
+        <v>1.8317</v>
       </c>
       <c r="G3" t="n">
         <v>2.1785</v>
@@ -688,13 +688,13 @@
         <v>2.2027</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8658</v>
+        <v>-0.1492</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8046</v>
+        <v>-0.261</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0612</v>
+        <v>0.1118</v>
       </c>
       <c r="V3" t="n">
         <v>0.3745</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. JOU COLL</t>
+          <t>D. CUEVAS SIMARRO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6614</v>
+        <v>3.3404</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7243</v>
+        <v>2.508</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9371</v>
+        <v>0.8324</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6597</v>
+        <v>0.9357</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4572</v>
+        <v>-0.8558</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7974</v>
+        <v>1.7914</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6478</v>
+        <v>2.3321</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7074</v>
+        <v>-0.3318</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0596</v>
+        <v>2.6639</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9881</v>
+        <v>-1.3964</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2503</v>
+        <v>-0.524</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7378</v>
+        <v>-0.8724</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7622</v>
+        <v>1.1014</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1014</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7622</v>
+        <v>2.2027</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2395</v>
+        <v>0.3695</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0765</v>
+        <v>-0.0266</v>
       </c>
       <c r="U4" t="n">
-        <v>0.163</v>
+        <v>0.3961</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.9339</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.3039</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. CUEVAS SIMARRO</t>
+          <t>G. JOU COLL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2742</v>
+        <v>2.2426</v>
       </c>
       <c r="E5" t="n">
-        <v>1.73</v>
+        <v>1.565</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5441</v>
+        <v>0.6777</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9357</v>
+        <v>0.6597</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8558</v>
+        <v>1.4572</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7914</v>
+        <v>-0.7974</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3321</v>
+        <v>1.6478</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3318</v>
+        <v>1.7074</v>
       </c>
       <c r="L5" t="n">
-        <v>2.6639</v>
+        <v>-0.0596</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3964</v>
+        <v>-0.9881</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.524</v>
+        <v>-0.2503</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8724</v>
+        <v>-0.7378</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1014</v>
+        <v>1.7622</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1014</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2027</v>
+        <v>1.7622</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6968</v>
+        <v>-0.1793</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8046</v>
+        <v>-0.0828</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1078</v>
+        <v>-0.0964</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9339</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.3039</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8583</v>
+        <v>0.7476</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6153</v>
+        <v>1.5622</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.757</v>
+        <v>-0.8147</v>
       </c>
       <c r="G6" t="n">
         <v>1.832</v>
@@ -922,13 +922,13 @@
         <v>0.8811</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7224</v>
+        <v>0.6116</v>
       </c>
       <c r="T6" t="n">
-        <v>0.517</v>
+        <v>0.4639</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2054</v>
+        <v>0.1477</v>
       </c>
       <c r="V6" t="n">
         <v>-0.3745</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. BARRO</t>
+          <t>J. CREMO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4079</v>
+        <v>0.2822</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4132</v>
+        <v>0.2464</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0053</v>
+        <v>0.0358</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.38</v>
+        <v>-1.2176</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6595</v>
+        <v>-1.3272</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7205</v>
+        <v>0.1096</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3054</v>
+        <v>0.2024</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1535</v>
+        <v>-0.7796</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1519</v>
+        <v>0.982</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.6854</v>
+        <v>-1.42</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8129999999999999</v>
+        <v>-0.5475</v>
       </c>
       <c r="O7" t="n">
         <v>-0.8724</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6608000000000001</v>
+        <v>1.1014</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2027</v>
+        <v>-1.1014</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5419</v>
+        <v>2.2027</v>
       </c>
       <c r="S7" t="n">
-        <v>1.1448</v>
+        <v>0.3984</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8216</v>
+        <v>0.0265</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3232</v>
+        <v>0.3719</v>
       </c>
       <c r="V7" t="n">
-        <v>1.3039</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4889</v>
+        <v>1.1189</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.185</v>
+        <v>-1.1189</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. CREMO</t>
+          <t>S. BARRO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4977</v>
+        <v>-0.2182</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6487000000000001</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1511</v>
+        <v>-0.1206</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.2176</v>
+        <v>-1.38</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.3272</v>
+        <v>-0.6595</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1096</v>
+        <v>-0.7205</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2024</v>
+        <v>0.3054</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7796</v>
+        <v>0.1535</v>
       </c>
       <c r="L8" t="n">
-        <v>0.982</v>
+        <v>0.1519</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.42</v>
+        <v>-1.6854</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5475</v>
+        <v>-0.8129999999999999</v>
       </c>
       <c r="O8" t="n">
         <v>-0.8724</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1014</v>
+        <v>-0.6608000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1014</v>
+        <v>-2.2027</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2027</v>
+        <v>1.5419</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3815</v>
+        <v>0.5187</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8687</v>
+        <v>0.3108</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4872</v>
+        <v>0.2079</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.3039</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1189</v>
+        <v>1.4889</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1189</v>
+        <v>-0.185</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5075</v>
+        <v>-1.7554</v>
       </c>
       <c r="E9" t="n">
-        <v>1.4486</v>
+        <v>0.5754</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.9561</v>
+        <v>-2.3308</v>
       </c>
       <c r="G9" t="n">
         <v>-2.5316</v>
@@ -1156,13 +1156,13 @@
         <v>0.2203</v>
       </c>
       <c r="S9" t="n">
-        <v>1.9889</v>
+        <v>0.7409</v>
       </c>
       <c r="T9" t="n">
-        <v>1.4262</v>
+        <v>0.553</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5626</v>
+        <v>0.1879</v>
       </c>
       <c r="V9" t="n">
         <v>-0.185</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6714</v>
+        <v>-1.9965</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6733</v>
+        <v>-2.2578</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0019</v>
+        <v>0.2613</v>
       </c>
       <c r="G11" t="n">
         <v>-1.588</v>
@@ -1312,13 +1312,13 @@
         <v>0.4405</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1846</v>
+        <v>-0.5097</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1719</v>
+        <v>0.2436</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.0127</v>
+        <v>-0.7533</v>
       </c>
       <c r="V11" t="n">
         <v>1.8634</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.5198</v>
+        <v>-4.6682</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.0768</v>
+        <v>-3.427</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.443</v>
+        <v>-1.2412</v>
       </c>
       <c r="G12" t="n">
         <v>-1.9065</v>
@@ -1390,13 +1390,13 @@
         <v>0.2203</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2433</v>
+        <v>-0.3917</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5203</v>
+        <v>0.1296</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.723</v>
+        <v>-0.5213</v>
       </c>
       <c r="V12" t="n">
         <v>-1.4889</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.293699999999999</v>
+        <v>4.574800000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>4.1554</v>
+        <v>5.436400000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.8615999999999999</v>
+        <v>-0.8615999999999994</v>
       </c>
       <c r="G13" t="n">
         <v>0.5782999999999998</v>
@@ -1447,13 +1447,13 @@
         <v>3.5606</v>
       </c>
       <c r="L13" t="n">
-        <v>1.9107</v>
+        <v>1.910699999999999</v>
       </c>
       <c r="M13" t="n">
         <v>-4.892899999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>0.03380000000000016</v>
+        <v>0.03379999999999994</v>
       </c>
       <c r="O13" t="n">
         <v>-4.926699999999999</v>
@@ -1468,13 +1468,13 @@
         <v>12.1149</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6405999999999992</v>
+        <v>1.9216</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9053000000000002</v>
+        <v>2.1865</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2646999999999996</v>
+        <v>-0.2646999999999997</v>
       </c>
       <c r="V13" t="n">
         <v>3.176199999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.3579</v>
+        <v>2.9112</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6666</v>
+        <v>1.018</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6913</v>
+        <v>1.8931</v>
       </c>
       <c r="G14" t="n">
         <v>0.4499</v>
@@ -1546,13 +1546,13 @@
         <v>0.8811</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3751</v>
+        <v>0.9283</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2327</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1424</v>
+        <v>0.3441</v>
       </c>
       <c r="V14" t="n">
         <v>1.7533</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8651</v>
+        <v>1.867</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1645</v>
+        <v>2.2817</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2994</v>
+        <v>-0.4147</v>
       </c>
       <c r="G15" t="n">
         <v>0.3888</v>
@@ -1624,13 +1624,13 @@
         <v>2.2027</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.105</v>
+        <v>-0.1031</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4079</v>
+        <v>-0.2907</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3029</v>
+        <v>0.1876</v>
       </c>
       <c r="V15" t="n">
         <v>2.6827</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>F. SCHOTT</t>
+          <t>E. VICEDO AYALA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4888</v>
+        <v>0.9550999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.6082</v>
+        <v>0.1363</v>
       </c>
       <c r="F16" t="n">
-        <v>1.097</v>
+        <v>0.8189</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.9163</v>
+        <v>0.5514</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7784</v>
+        <v>-0.0692</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.138</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1677</v>
+        <v>1.217</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.09810000000000001</v>
+        <v>0.7286</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2658</v>
+        <v>0.4884</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.084</v>
+        <v>-0.6656</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6802</v>
+        <v>-0.7978</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4038</v>
+        <v>0.1322</v>
       </c>
       <c r="P16" t="n">
-        <v>1.7622</v>
+        <v>1.9825</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7622</v>
+        <v>1.9825</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2469</v>
+        <v>-0.5347</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9608</v>
+        <v>-0.7062</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7139</v>
+        <v>0.1716</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1101</v>
+        <v>-1.044</v>
       </c>
       <c r="W16" t="n">
-        <v>0.185</v>
+        <v>-0.3745</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2951</v>
+        <v>-0.6696</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. VICEDO AYALA</t>
+          <t>F. SCHOTT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2568</v>
+        <v>0.7948</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5667</v>
+        <v>-0.2567</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8235</v>
+        <v>1.0514</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5514</v>
+        <v>-0.9163</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0692</v>
+        <v>-0.7784</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6205000000000001</v>
+        <v>-0.138</v>
       </c>
       <c r="J17" t="n">
-        <v>1.217</v>
+        <v>0.1677</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7286</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4884</v>
+        <v>0.2658</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6656</v>
+        <v>-1.084</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7978</v>
+        <v>-0.6802</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1322</v>
+        <v>-0.4038</v>
       </c>
       <c r="P17" t="n">
-        <v>1.9825</v>
+        <v>1.7622</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9825</v>
+        <v>1.7622</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.233</v>
+        <v>0.059</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.4092</v>
+        <v>-0.6093</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1762</v>
+        <v>0.6683</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.044</v>
+        <v>-0.1101</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3745</v>
+        <v>0.185</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6696</v>
+        <v>-0.2951</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. SOLA IDDRISU</t>
+          <t>J. CONE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.08409999999999999</v>
+        <v>0.6485</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3427</v>
+        <v>1.6901</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2586</v>
+        <v>-1.0416</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0916</v>
+        <v>3.444</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.7613</v>
+        <v>-0.5266999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>1.853</v>
+        <v>3.9708</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1859</v>
+        <v>2.8243</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.0492</v>
+        <v>-0.7451</v>
       </c>
       <c r="L18" t="n">
-        <v>2.2351</v>
+        <v>3.5694</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0942</v>
+        <v>0.6197</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7121</v>
+        <v>0.2184</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3821</v>
+        <v>0.4014</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2203</v>
+        <v>-0.6608000000000001</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2027</v>
+        <v>-1.1014</v>
       </c>
       <c r="R18" t="n">
-        <v>2.423</v>
+        <v>0.4405</v>
       </c>
       <c r="S18" t="n">
-        <v>1.1906</v>
+        <v>0.1031</v>
       </c>
       <c r="T18" t="n">
-        <v>1.6151</v>
+        <v>-0.0328</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4245</v>
+        <v>0.136</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.4185</v>
+        <v>-2.2378</v>
       </c>
       <c r="W18" t="n">
-        <v>0.7444</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.1629</v>
+        <v>-2.2378</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. WEMBI</t>
+          <t>A. SOLA IDDRISU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.015</v>
+        <v>-0.5036</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0485</v>
+        <v>0.1711</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.0334</v>
+        <v>-0.6747</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.0658</v>
+        <v>0.0916</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.2014</v>
+        <v>-1.7613</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1355</v>
+        <v>1.853</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.0791</v>
+        <v>1.1859</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.193</v>
+        <v>-1.0492</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1139</v>
+        <v>2.2351</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0133</v>
+        <v>-1.0942</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.7121</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0216</v>
+        <v>-0.3821</v>
       </c>
       <c r="P19" t="n">
-        <v>0.8811</v>
+        <v>0.2203</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.2027</v>
       </c>
       <c r="R19" t="n">
-        <v>0.8811</v>
+        <v>2.423</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9487</v>
+        <v>0.603</v>
       </c>
       <c r="T19" t="n">
-        <v>1.6386</v>
+        <v>0.4435</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6899999999999999</v>
+        <v>0.1595</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.7489</v>
+        <v>-1.4185</v>
       </c>
       <c r="W19" t="n">
-        <v>1.4889</v>
+        <v>0.7444</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.2378</v>
+        <v>-2.1629</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. CONE</t>
+          <t>V. ARTEAGA GONZALEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1716</v>
+        <v>-0.6859</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3386</v>
+        <v>0.4085</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5102</v>
+        <v>-1.0944</v>
       </c>
       <c r="G20" t="n">
-        <v>3.444</v>
+        <v>-0.0055</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5266999999999999</v>
+        <v>-0.0055</v>
       </c>
       <c r="I20" t="n">
-        <v>3.9708</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>2.8243</v>
+        <v>0.018</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7451</v>
+        <v>0.018</v>
       </c>
       <c r="L20" t="n">
-        <v>3.5694</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6197</v>
+        <v>-0.0235</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2184</v>
+        <v>-0.0235</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4014</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.6608000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1014</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4405</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.717</v>
+        <v>0.4386</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3843</v>
+        <v>0.3905</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3327</v>
+        <v>0.048</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.2378</v>
+        <v>-1.1189</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.2378</v>
+        <v>-1.1189</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V. ARTEAGA GONZALEZ</t>
+          <t>E. WEMBI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.949</v>
+        <v>-0.8153</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1742</v>
+        <v>0.8768</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1232</v>
+        <v>-1.6922</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0055</v>
+        <v>-1.0658</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0055</v>
+        <v>-1.2014</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>0.1355</v>
       </c>
       <c r="J21" t="n">
-        <v>0.018</v>
+        <v>-1.0791</v>
       </c>
       <c r="K21" t="n">
-        <v>0.018</v>
+        <v>-1.193</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.1139</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0235</v>
+        <v>0.0133</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0235</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>0.0216</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.8811</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.8811</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1754</v>
+        <v>0.1183</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1562</v>
+        <v>0.467</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0192</v>
+        <v>-0.3487</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.1189</v>
+        <v>-0.7489</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.4889</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.1189</v>
+        <v>-2.2378</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6189</v>
+        <v>-1.7123</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1626</v>
+        <v>-0.8111</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4563</v>
+        <v>-0.9012</v>
       </c>
       <c r="G22" t="n">
         <v>-0.0733</v>
@@ -2170,13 +2170,13 @@
         <v>1.9825</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.5764</v>
+        <v>-0.6698</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8968</v>
+        <v>-0.5453</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6796</v>
+        <v>-0.1245</v>
       </c>
       <c r="V22" t="n">
         <v>-0.7489</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.622</v>
+        <v>-4.41</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.5361</v>
+        <v>-4.6533</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0859</v>
+        <v>0.2433</v>
       </c>
       <c r="G23" t="n">
         <v>-3.4431</v>
@@ -2248,13 +2248,13 @@
         <v>0.6608000000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>0.548</v>
+        <v>0.76</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6811</v>
+        <v>0.5639</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1331</v>
+        <v>0.1961</v>
       </c>
       <c r="V23" t="n">
         <v>-0.185</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2938</v>
+        <v>-0.9504999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8614999999999995</v>
+        <v>0.8613999999999997</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.155199999999999</v>
+        <v>-1.8121</v>
       </c>
       <c r="G24" t="n">
         <v>-0.5783000000000005</v>
@@ -2296,13 +2296,13 @@
         <v>-3.5945</v>
       </c>
       <c r="I24" t="n">
-        <v>3.0161</v>
+        <v>3.016100000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>4.893</v>
+        <v>4.893000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.03399999999999999</v>
+        <v>-0.03399999999999954</v>
       </c>
       <c r="L24" t="n">
         <v>4.9267</v>
@@ -2326,16 +2326,16 @@
         <v>13.2164</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6405000000000001</v>
+        <v>1.7027</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2647000000000004</v>
+        <v>0.2647999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.9053</v>
+        <v>1.438</v>
       </c>
       <c r="V24" t="n">
-        <v>-3.176100000000001</v>
+        <v>-3.1761</v>
       </c>
       <c r="W24" t="n">
         <v>7.8189</v>
